--- a/Input/Takaful_Nas/benefits.xlsx
+++ b/Input/Takaful_Nas/benefits.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="136">
   <si>
     <t xml:space="preserve">PlanName</t>
   </si>
@@ -43,7 +43,7 @@
     <t xml:space="preserve">Chronic Condition Cover</t>
   </si>
   <si>
-    <t xml:space="preserve">Pre-existing Condition Cover</t>
+    <t xml:space="preserve">Pre-existing Cover</t>
   </si>
   <si>
     <t xml:space="preserve">Accommodation Type</t>
@@ -214,7 +214,7 @@
     <t xml:space="preserve">AED 1,000,000</t>
   </si>
   <si>
-    <t xml:space="preserve">Worldwide Including USA</t>
+    <t xml:space="preserve">Worldwide including USA</t>
   </si>
   <si>
     <t xml:space="preserve">NAS CN</t>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worldwide Including USA</t>
   </si>
   <si>
     <t xml:space="preserve">10%</t>
@@ -443,7 +446,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -470,6 +473,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -514,7 +522,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -523,7 +531,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -560,7 +576,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="58" style="0" width="11.52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="80.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,7 +598,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -675,14 +691,14 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2"/>
+      <c r="AM1" s="3"/>
       <c r="AN1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="AO1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="2"/>
+      <c r="AP1" s="3"/>
       <c r="AQ1" s="1" t="s">
         <v>40</v>
       </c>
@@ -695,7 +711,7 @@
       <c r="AT1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AU1" s="2"/>
+      <c r="AU1" s="3"/>
       <c r="AV1" s="1" t="s">
         <v>44</v>
       </c>
@@ -758,13 +774,13 @@
       <c r="B2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="2"/>
+      <c r="E2" s="3"/>
       <c r="F2" s="1" t="s">
         <v>66</v>
       </c>
@@ -792,7 +808,7 @@
       <c r="N2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="O2" s="2"/>
+      <c r="O2" s="3"/>
       <c r="P2" s="1" t="s">
         <v>73</v>
       </c>
@@ -814,7 +830,7 @@
       <c r="V2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="W2" s="2"/>
+      <c r="W2" s="3"/>
       <c r="X2" s="1" t="s">
         <v>80</v>
       </c>
@@ -827,14 +843,14 @@
       <c r="AA2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AB2" s="2"/>
+      <c r="AB2" s="3"/>
       <c r="AC2" s="1" t="s">
         <v>84</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AE2" s="2"/>
+      <c r="AE2" s="3"/>
       <c r="AF2" s="1" t="s">
         <v>86</v>
       </c>
@@ -853,16 +869,16 @@
       <c r="AK2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
       <c r="AN2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AO2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
+      <c r="AP2" s="3"/>
+      <c r="AQ2" s="3"/>
       <c r="AR2" s="1" t="s">
         <v>92</v>
       </c>
@@ -872,71 +888,68 @@
       <c r="AT2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="AU2" s="2"/>
-      <c r="AV2" s="2"/>
+      <c r="AU2" s="3"/>
+      <c r="AV2" s="3"/>
       <c r="AW2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AX2" s="3" t="s">
         <v>93</v>
       </c>
+      <c r="AX2" s="5" t="s">
+        <v>94</v>
+      </c>
       <c r="AY2" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AZ2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BA2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BC2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="BA2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BB2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BC2" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="BD2" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="BF2" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="BG2" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="BH2" s="0" t="s">
-        <v>92</v>
+      <c r="BG2" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="BI2" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="BJ2" s="1" t="s">
         <v>64</v>
       </c>
       <c r="BK2" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BM2" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="49.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="1" t="s">
         <v>66</v>
       </c>
@@ -964,9 +977,9 @@
       <c r="N3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="O3" s="2"/>
+      <c r="O3" s="3"/>
       <c r="P3" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q3" s="1" t="s">
         <v>74</v>
@@ -975,7 +988,7 @@
         <v>75</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>77</v>
@@ -984,9 +997,9 @@
         <v>78</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W3" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="W3" s="3"/>
       <c r="X3" s="1" t="s">
         <v>80</v>
       </c>
@@ -999,14 +1012,14 @@
       <c r="AA3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AB3" s="2"/>
+      <c r="AB3" s="3"/>
       <c r="AC3" s="1" t="s">
         <v>84</v>
       </c>
       <c r="AD3" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AE3" s="2"/>
+      <c r="AE3" s="3"/>
       <c r="AF3" s="1" t="s">
         <v>86</v>
       </c>
@@ -1014,7 +1027,7 @@
         <v>87</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AI3" s="1" t="s">
         <v>89</v>
@@ -1025,16 +1038,16 @@
       <c r="AK3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AL3" s="2"/>
-      <c r="AM3" s="2"/>
+      <c r="AL3" s="3"/>
+      <c r="AM3" s="3"/>
       <c r="AN3" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AO3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AP3" s="2"/>
-      <c r="AQ3" s="2"/>
+      <c r="AP3" s="3"/>
+      <c r="AQ3" s="3"/>
       <c r="AR3" s="1" t="s">
         <v>92</v>
       </c>
@@ -1044,47 +1057,47 @@
       <c r="AT3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="AU3" s="2"/>
-      <c r="AV3" s="2"/>
+      <c r="AU3" s="3"/>
+      <c r="AV3" s="3"/>
       <c r="AW3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AX3" s="3" t="s">
         <v>93</v>
       </c>
+      <c r="AX3" s="5" t="s">
+        <v>94</v>
+      </c>
       <c r="AY3" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AZ3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BA3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BC3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="BA3" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BB3" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BC3" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="BD3" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="49.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="E4" s="3"/>
       <c r="F4" s="1" t="s">
         <v>66</v>
       </c>
@@ -1112,18 +1125,18 @@
       <c r="N4" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="O4" s="2"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>77</v>
@@ -1132,11 +1145,11 @@
         <v>78</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="W4" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="W4" s="3"/>
       <c r="X4" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y4" s="1" t="s">
         <v>81</v>
@@ -1147,25 +1160,25 @@
       <c r="AA4" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AB4" s="2"/>
+      <c r="AB4" s="3"/>
       <c r="AC4" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AD4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AE4" s="2"/>
+      <c r="AE4" s="3"/>
       <c r="AF4" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG4" s="1" t="s">
         <v>87</v>
       </c>
       <c r="AH4" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AJ4" s="1" t="s">
         <v>90</v>
@@ -1173,16 +1186,16 @@
       <c r="AK4" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2"/>
+      <c r="AL4" s="3"/>
+      <c r="AM4" s="3"/>
       <c r="AN4" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AO4" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AP4" s="2"/>
-      <c r="AQ4" s="2"/>
+      <c r="AP4" s="3"/>
+      <c r="AQ4" s="3"/>
       <c r="AR4" s="1" t="s">
         <v>92</v>
       </c>
@@ -1192,47 +1205,47 @@
       <c r="AT4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="AU4" s="2"/>
-      <c r="AV4" s="2"/>
+      <c r="AU4" s="3"/>
+      <c r="AV4" s="3"/>
       <c r="AW4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AX4" s="3" t="s">
         <v>93</v>
       </c>
+      <c r="AX4" s="5" t="s">
+        <v>94</v>
+      </c>
       <c r="AY4" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AZ4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BA4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BC4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="BA4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BB4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BC4" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="BD4" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="E5" s="3"/>
       <c r="F5" s="1" t="s">
         <v>66</v>
       </c>
@@ -1260,18 +1273,18 @@
       <c r="N5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="O5" s="2"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>77</v>
@@ -1280,11 +1293,11 @@
         <v>78</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="W5" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="W5" s="3"/>
       <c r="X5" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y5" s="1" t="s">
         <v>81</v>
@@ -1295,25 +1308,25 @@
       <c r="AA5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AB5" s="2"/>
+      <c r="AB5" s="3"/>
       <c r="AC5" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AD5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AE5" s="2"/>
+      <c r="AE5" s="3"/>
       <c r="AF5" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG5" s="1" t="s">
         <v>87</v>
       </c>
       <c r="AH5" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AJ5" s="1" t="s">
         <v>90</v>
@@ -1321,16 +1334,16 @@
       <c r="AK5" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AL5" s="2"/>
-      <c r="AM5" s="2"/>
+      <c r="AL5" s="3"/>
+      <c r="AM5" s="3"/>
       <c r="AN5" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AO5" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AP5" s="2"/>
-      <c r="AQ5" s="2"/>
+      <c r="AP5" s="3"/>
+      <c r="AQ5" s="3"/>
       <c r="AR5" s="1" t="s">
         <v>92</v>
       </c>
@@ -1340,47 +1353,47 @@
       <c r="AT5" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="AU5" s="2"/>
-      <c r="AV5" s="2"/>
+      <c r="AU5" s="3"/>
+      <c r="AV5" s="3"/>
       <c r="AW5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AX5" s="3" t="s">
         <v>93</v>
       </c>
+      <c r="AX5" s="5" t="s">
+        <v>94</v>
+      </c>
       <c r="AY5" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AZ5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BA5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BC5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="BA5" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BB5" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BC5" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="BD5" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="E6" s="3"/>
       <c r="F6" s="1" t="s">
         <v>66</v>
       </c>
@@ -1391,7 +1404,7 @@
         <v>68</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>70</v>
@@ -1408,18 +1421,18 @@
       <c r="N6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="O6" s="2"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>77</v>
@@ -1428,11 +1441,11 @@
         <v>78</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="W6" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="W6" s="3"/>
       <c r="X6" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y6" s="1" t="s">
         <v>81</v>
@@ -1443,14 +1456,14 @@
       <c r="AA6" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AB6" s="2"/>
+      <c r="AB6" s="3"/>
       <c r="AC6" s="1" t="s">
         <v>90</v>
       </c>
       <c r="AD6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="AE6" s="2"/>
+      <c r="AE6" s="3"/>
       <c r="AF6" s="1" t="s">
         <v>90</v>
       </c>
@@ -1469,16 +1482,16 @@
       <c r="AK6" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AL6" s="2"/>
-      <c r="AM6" s="2"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3"/>
       <c r="AN6" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AO6" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AP6" s="2"/>
-      <c r="AQ6" s="2"/>
+      <c r="AP6" s="3"/>
+      <c r="AQ6" s="3"/>
       <c r="AR6" s="1" t="s">
         <v>92</v>
       </c>
@@ -1488,31 +1501,31 @@
       <c r="AT6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="AU6" s="2"/>
-      <c r="AV6" s="2"/>
+      <c r="AU6" s="3"/>
+      <c r="AV6" s="3"/>
       <c r="AW6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AX6" s="3" t="s">
         <v>93</v>
       </c>
+      <c r="AX6" s="5" t="s">
+        <v>94</v>
+      </c>
       <c r="AY6" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AZ6" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BA6" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="BA6" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="BB6" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BC6" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BD6" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
